--- a/medical_school_costs_template - Copy.xlsx
+++ b/medical_school_costs_template - Copy.xlsx
@@ -2,13 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/537f6ece77514512/Desktop/Utilities/loans/debt_calculator_python/input/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="11_A2E024A5EC40C6BAEC44E4012A4FF01AE176DC25" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F464730-CB29-43AF-A73E-F25835FA3E47}"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_A2E024A5EC40C6BAEC44E4012A4FF01AE176DC25" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1240F9D2-3D5D-4C70-A7AE-A6595F5A52F2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -256,6 +251,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
